--- a/gantt/Gantt_live_11DP-C.xlsx
+++ b/gantt/Gantt_live_11DP-C.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ettore/AI/ClaudeCode/BBI/IB/IB_Project/Submission/Freshman_version/plan_v2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ettore/AI/ClaudeCode/BBI/IB/IB_Project/Submission/2026.10.20_corrections/repo/status/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C98A9B-1FAA-9C4F-9FD4-4B963B1F29F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF45DA8-E833-BC4C-A433-DA12B450F61E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -252,7 +252,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="424">
   <si>
     <t>Project Status · Group 11DP-C · Pyruvate Kinase Deficiency</t>
   </si>
@@ -356,69 +356,93 @@
     <t>1.2 Review and commit the overview and team section (PKD_2); submit the repository URL on Moodle</t>
   </si>
   <si>
+    <t>PKD_2 committed by Aarón on 8 Oct; repository URL submitted on Moodle by Ettore on 9 Oct.</t>
+  </si>
+  <si>
+    <t>1.3 Review and commit the Gantt chart (PKD_3)</t>
+  </si>
+  <si>
+    <t>Bruno</t>
+  </si>
+  <si>
+    <t>Committed by Leo on 8 Oct and edited by Pol; owner after the role swap: Bruno.</t>
+  </si>
+  <si>
+    <t>1.4 Review and commit the task details (PKD_4)</t>
+  </si>
+  <si>
+    <t>Pol</t>
+  </si>
+  <si>
+    <t>Committed by Pol on 8 Oct; owner columns corrected for the role swap.</t>
+  </si>
+  <si>
+    <t>1.5 Review and commit the risk analysis and references (PKD_5, PKD_6)</t>
+  </si>
+  <si>
+    <t>Committed by Bruno (PKD_6 on 8 Oct, PKD_5 on 9 Oct), references updated by Ettore on 9 Oct; owner after the role swap: Leo.</t>
+  </si>
+  <si>
+    <t>1.6 Create the Project Status document</t>
+  </si>
+  <si>
+    <t>Created by Ettore on 9 Oct (status/Project_Status_2026_10_09.md).</t>
+  </si>
+  <si>
+    <t>1.7 Weekly status update and team meeting (Fridays 16 and 23 Oct)</t>
+  </si>
+  <si>
     <t>In progress</t>
   </si>
   <si>
-    <t>PKD_2 committed by Aarón on 8 Oct (roles of Bruno and Leo swapped by team decision); Moodle URL submission to be confirmed.</t>
-  </si>
-  <si>
-    <t>1.3 Review and commit the Gantt chart (PKD_3)</t>
-  </si>
-  <si>
-    <t>Bruno</t>
-  </si>
-  <si>
-    <t>Committed by Leo on 8 Oct and edited by Pol; owner after the role swap: Bruno.</t>
-  </si>
-  <si>
-    <t>1.4 Review and commit the task details (PKD_4)</t>
-  </si>
-  <si>
-    <t>Pol</t>
-  </si>
-  <si>
-    <t>Committed by Pol on 8 Oct; owner columns corrected for the role swap.</t>
-  </si>
-  <si>
-    <t>1.5 Review and commit the risk analysis and references (PKD_5, PKD_6)</t>
-  </si>
-  <si>
-    <t>Committed by Bruno (PKD_6 on 8 Oct, PKD_5 on 9 Oct), references updated by Ettore on 9 Oct; owner after the role swap: Leo.</t>
-  </si>
-  <si>
-    <t>1.6 Create the Project Status document</t>
+    <t>Meeting of 16 Oct held; next meeting 23 Oct.</t>
+  </si>
+  <si>
+    <t>1.8 Prepare the Project Status document for the 22 Oct discussion</t>
+  </si>
+  <si>
+    <t>This update, for the class discussion of 22 Oct.</t>
+  </si>
+  <si>
+    <t>1.9 Produce the final Gantt chart with real dates (live version)</t>
   </si>
   <si>
     <t>Pending</t>
   </si>
   <si>
-    <t>1.7 Weekly status update and team meeting (Fridays 16 and 23 Oct)</t>
-  </si>
-  <si>
-    <t>1.8 Prepare the Project Status document for the 22 Oct discussion</t>
-  </si>
-  <si>
-    <t>1.9 Produce the final Gantt chart with real dates (live version)</t>
-  </si>
-  <si>
     <t>WP2 · Data sources, literature, and sequences</t>
   </si>
   <si>
     <t>2.1 Characterize the supplied sequences: translate both CDSs, compare wild type and mutant, and name the variant in HGVS nomenclature</t>
   </si>
   <si>
+    <t>Variant c.1456C&gt;T, p.Arg486Trp (missense) identified in the sequence alignment lab (lab/Lab_1_.md); translation of both CDSs to be documented.</t>
+  </si>
+  <si>
     <t>2.2 Identify the gene, the isoform, and the reference entries (HGNC, NCBI Gene, UniProt)</t>
   </si>
   <si>
+    <t>NCBI Gene 5313, RefSeq NM_000298.6 and NP_000289.1, and OMIM recorded in lab/Lab_1_.md; HGNC:9020 and UniProt P30613 to be added.</t>
+  </si>
+  <si>
     <t>2.3 Collect clinical and population evidence on the variant (ClinVar, gnomAD, OMIM, literature)</t>
   </si>
   <si>
+    <t>Incident</t>
+  </si>
+  <si>
+    <t>New dates to be set at the team meeting of 21 Oct.</t>
+  </si>
+  <si>
     <t>2.4 Review the literature on PK and PKD: normal function, mechanism, inheritance, and clinical features</t>
   </si>
   <si>
     <t>2.5 Retrieve the reviewed orthologous sequences: rat, mouse, and dog (outgroup)</t>
   </si>
   <si>
+    <t>Rat PKLR (NM_012624.3, NP_036756.3) recorded in lab/Lab_1_.md; mouse and dog PKLR to be retrieved.</t>
+  </si>
+  <si>
     <t>2.6 Select the experimental structures: wild-type and mutant human R-type PK; rat PK</t>
   </si>
   <si>
@@ -428,27 +452,45 @@
     <t>2.8 Verify the sequence characterization independently: repeat the translation and the comparison of the four files</t>
   </si>
   <si>
+    <t>Follows 2.1. New dates to be set at the team meeting of 21 Oct.</t>
+  </si>
+  <si>
     <t>WP3 · Sequence and structure analysis</t>
   </si>
   <si>
     <t>3.1 Pairwise alignments of human PK with the rat and mouse orthologs (protein and CDS)</t>
   </si>
   <si>
+    <t>Started in the sequence alignment lab (lab/Lab_1_.md); to be completed with the PKLR sequences of rat and mouse.</t>
+  </si>
+  <si>
     <t>3.2 Multiple sequence alignment of human, rat, mouse, and dog PK; conservation of the substituted position and lineage of each difference</t>
   </si>
   <si>
+    <t>Follows 2.5. New dates to be set at the team meeting of 21 Oct.</t>
+  </si>
+  <si>
     <t>3.3 Map the substituted residue on the wild-type structure: distances to the active site, the allosteric site, and the domain and subunit interfaces</t>
   </si>
   <si>
+    <t>Follows 2.6. New dates to be set at the team meeting of 21 Oct.</t>
+  </si>
+  <si>
     <t>3.4 Superpose the wild-type and mutant structures (repeated in the 22 Oct lab)</t>
   </si>
   <si>
+    <t>Scheduled for the structure superposition lab of 22 Oct.</t>
+  </si>
+  <si>
     <t>3.5 Compare the human R-type and rat L-type structures around the substituted position</t>
   </si>
   <si>
     <t>3.6 Assess pathogenicity: combine clinical, population, conservation, structural, and biochemical evidence</t>
   </si>
   <si>
+    <t>Follows 2.3 and 3.2. New dates to be set at the team meeting of 21 Oct.</t>
+  </si>
+  <si>
     <t>3.7 Explain the impact on the patient: from enzyme activity to red-cell ATP, haemolysis, and clinical severity</t>
   </si>
   <si>
@@ -519,9 +561,6 @@
   </si>
   <si>
     <t>Finished; Real Finish Date filled</t>
-  </si>
-  <si>
-    <t>Incident</t>
   </si>
   <si>
     <t>A problem occurred; describe it and the workaround in Notes</t>
@@ -1237,36 +1276,54 @@
     <t>Incidents</t>
   </si>
   <si>
+    <t>GitHub username</t>
+  </si>
+  <si>
     <t>Aarón Godino Martínez</t>
   </si>
   <si>
     <t>Product Owner</t>
   </si>
   <si>
+    <t>Idonthaveanyideafornames</t>
+  </si>
+  <si>
     <t>Bruno Carrasquilla</t>
   </si>
   <si>
     <t>Sequence Analyst</t>
   </si>
   <si>
+    <t>BrunoCarrasquilla</t>
+  </si>
+  <si>
     <t>Ettore Colombo</t>
   </si>
   <si>
     <t>Project Manager</t>
   </si>
   <si>
+    <t>AIHector</t>
+  </si>
+  <si>
     <t>Leo Nader Al Hourani</t>
   </si>
   <si>
     <t>Data and GitHub Manager</t>
   </si>
   <si>
+    <t>XxNaderTheKing08Xx</t>
+  </si>
+  <si>
     <t>Pol Monllau</t>
   </si>
   <si>
     <t>Structure Analyst</t>
   </si>
   <si>
+    <t>polmonllau</t>
+  </si>
+  <si>
     <t>Total</t>
   </si>
   <si>
@@ -1378,100 +1435,88 @@
     <t>R1</t>
   </si>
   <si>
-    <t>Commits made in bulk or near the deadlines</t>
-  </si>
-  <si>
-    <t>Partly occurred</t>
-  </si>
-  <si>
-    <t>Section-by-section commits on 9 Oct (1.1–1.5); commit after every work session; history reviewed weekly (1.7).</t>
+    <t>GitHub unavailable or access problems near a deadline</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>Finish each delivery one day early; local clone on every computer; commit after every work session; tell the instructors with evidence of the outage.</t>
+  </si>
+  <si>
+    <t>External risk register revised after the instructor's feedback (12 Oct).</t>
   </si>
   <si>
     <t>R2</t>
   </si>
   <si>
-    <t>Unequal contribution among members</t>
-  </si>
-  <si>
-    <t>Seven tasks per member; own commits; contributions recorded weekly; Authors' contributions section.</t>
+    <t>Public databases (UniProt, PDB, NCBI) unavailable, or their records updated or superseded during the project</t>
+  </si>
+  <si>
+    <t>Record every accession with its access date; archive the files used in the repository; check the current record before citing; use a mirror or an alternative database.</t>
   </si>
   <si>
     <t>R3</t>
   </si>
   <si>
-    <t>Repository structure not compliant with the requirements</t>
-  </si>
-  <si>
-    <t>Occurred</t>
-  </si>
-  <si>
-    <t>Create report/, status/, gantt/, references/ on 9 Oct (1.1); check weekly (1.7).</t>
+    <t>Illness or unforeseen personal circumstances make a member unavailable</t>
+  </si>
+  <si>
+    <t>A second member knows the status of every task; tasks documented in the Project Status; pending tasks redistributed at the weekly meeting; Gantt chart updated.</t>
   </si>
   <si>
     <t>R4</t>
   </si>
   <si>
-    <t>Project Status document or live Gantt chart not kept up to date</t>
-  </si>
-  <si>
-    <t>Open</t>
-  </si>
-  <si>
-    <t>Status document from 13 Oct (1.6); weekly update (1.7); final chart with real dates (1.9).</t>
+    <t>Exams and deadlines from other courses overlap with the project period</t>
+  </si>
+  <si>
+    <t>Collect each member's exam dates; schedule heavy tasks away from them; two days of margin before each delivery; rebalance tasks when a conflict appears.</t>
   </si>
   <si>
     <t>R5</t>
   </si>
   <si>
-    <t>Incorrect database record selected, or result misinterpreted</t>
-  </si>
-  <si>
-    <t>Reviewed entries only; accession, access date and rationale recorded (2.2, 2.5, 2.6); second-member check, including the variant table (2.8).</t>
+    <t>Online analysis tools or servers (alignment, structure viewers) unavailable, overloaded, or changed</t>
+  </si>
+  <si>
+    <t>Run each analysis soon after its lab; know an alternative tool; save inputs and parameters; export every result to the repository.</t>
   </si>
   <si>
     <t>R6</t>
   </si>
   <si>
-    <t>Alignment or structural results misinterpreted</t>
-  </si>
-  <si>
-    <t>Each analysis after its lab; questions to instructors; alignment repeated by a second member (3.9); superposition repeated in the 22 Oct lab (3.4).</t>
+    <t>Little published evidence, or no experimental structures, for the variants or species studied; articles behind paywalls</t>
+  </si>
+  <si>
+    <t>Search early; university library access; open-access articles and reviews for context; predicted structures, stated as such; justify any topic left out.</t>
   </si>
   <si>
     <t>R7</t>
   </si>
   <si>
-    <t>Species comparison insufficiently justified, or evolutionary changes inferred without an outgroup</t>
-  </si>
-  <si>
-    <t>Reason for each species stated; dog as outgroup (2.5, 3.2); lineage claims only when the outgroup supports them.</t>
+    <t>Course requirements, deadlines, or instructions changed or clarified during the project</t>
+  </si>
+  <si>
+    <t>Check announcements and documents at every weekly meeting; ask the instructors about ambiguities; record confirmed dates; adapt the plan.</t>
   </si>
   <si>
     <t>R8</t>
   </si>
   <si>
-    <t>Parts developed in isolation; members aware only of their own tasks</t>
-  </si>
-  <si>
-    <t>Synthesis meeting (3.8); full read-through (4.7); each member presents their own part (4.10–4.14); cross-questioning rehearsal (4.16).</t>
+    <t>A practical session (8, 15, or 22 October) cancelled or rescheduled</t>
+  </si>
+  <si>
+    <t>Learn the method from the course materials and tutoring hours; move the dependent task to the first available date.</t>
   </si>
   <si>
     <t>R9</t>
   </si>
   <si>
-    <t>Statements supported by weak or unverified sources, including GenAI output</t>
-  </si>
-  <si>
-    <t>Primary articles for facts, reviews for context; GenAI output verified at source; sources archived (2.7).</t>
-  </si>
-  <si>
-    <t>R10</t>
-  </si>
-  <si>
-    <t>Report format, length limits, or delivery deadline not met</t>
-  </si>
-  <si>
-    <t>Word budget; format check 27 Oct (4.8); assembly 26 Oct (4.6); final commit by 12:00 on 28 Oct (4.9).</t>
+    <t>Failure of a member's computer or internet connection</t>
+  </si>
+  <si>
+    <t>Keep all work in the remote repository; use university computers or a teammate's device; reassign the affected task if needed.</t>
   </si>
   <si>
     <t>Date</t>
@@ -1494,14 +1539,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="165" formatCode="ddd\ dd\ mmm\ yyyy"/>
-    <numFmt numFmtId="166" formatCode="dd\ mmm"/>
-    <numFmt numFmtId="167" formatCode="d"/>
-    <numFmt numFmtId="168" formatCode="ddd\ dd\ mmm"/>
-    <numFmt numFmtId="169" formatCode="dd\.mm"/>
-    <numFmt numFmtId="170" formatCode="dd\ mmm\ yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd\.mm"/>
+    <numFmt numFmtId="165" formatCode="d"/>
+    <numFmt numFmtId="166" formatCode="ddd\ dd\ mmm"/>
+    <numFmt numFmtId="167" formatCode="ddd\ dd\ mmm\ yyyy"/>
+    <numFmt numFmtId="168" formatCode="dd\ mmm\ yyyy"/>
+    <numFmt numFmtId="169" formatCode="dd\ mmm"/>
   </numFmts>
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1709,6 +1754,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="15">
     <fill>
@@ -1885,7 +1936,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1907,7 +1958,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="23" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="23" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1920,10 +1971,10 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1964,10 +2015,10 @@
     <xf numFmtId="0" fontId="27" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="28" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1975,7 +2026,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1991,16 +2042,16 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -2017,8 +2068,8 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2026,13 +2077,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="170" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -3009,116 +3061,116 @@
     <col min="1" max="1" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" s="3"/>
     </row>
-    <row r="4" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="28" x14ac:dyDescent="0.2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" ht="28" x14ac:dyDescent="0.2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" ht="28" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" ht="28" x14ac:dyDescent="0.2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" s="3"/>
     </row>
-    <row r="17" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" ht="28" x14ac:dyDescent="0.2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" s="3"/>
     </row>
-    <row r="21" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" ht="28" x14ac:dyDescent="0.2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" ht="56" x14ac:dyDescent="0.2">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="56" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -3141,17 +3193,17 @@
     <col min="8" max="8" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="9">
-        <v>46304</v>
+        <v>46315</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>2</v>
@@ -3419,7 +3471,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="28" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="14" t="s">
         <v>29</v>
       </c>
@@ -3459,7 +3511,7 @@
       <c r="G15" s="24"/>
       <c r="H15" s="24"/>
     </row>
-    <row r="16" spans="1:8" ht="28" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="14" t="s">
         <v>31</v>
       </c>
@@ -3487,7 +3539,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="28" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="14" t="s">
         <v>33</v>
       </c>
@@ -3505,20 +3557,22 @@
       <c r="E17" s="17">
         <v>46303</v>
       </c>
-      <c r="F17" s="17"/>
+      <c r="F17" s="17">
+        <v>46304</v>
+      </c>
       <c r="G17" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="H17" s="19" t="s">
+    </row>
+    <row r="18" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="14" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" ht="28" x14ac:dyDescent="0.2">
-      <c r="A18" s="14" t="s">
+      <c r="B18" s="25" t="s">
         <v>36</v>
-      </c>
-      <c r="B18" s="25" t="s">
-        <v>37</v>
       </c>
       <c r="C18" s="16">
         <f>Tasks!H18</f>
@@ -3538,15 +3592,15 @@
         <v>14</v>
       </c>
       <c r="H18" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="26" t="s">
         <v>39</v>
-      </c>
-      <c r="B19" s="26" t="s">
-        <v>40</v>
       </c>
       <c r="C19" s="16">
         <f>Tasks!H19</f>
@@ -3566,12 +3620,12 @@
         <v>14</v>
       </c>
       <c r="H19" s="19" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="14" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="28" x14ac:dyDescent="0.2">
-      <c r="A20" s="14" t="s">
-        <v>42</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>13</v>
@@ -3594,12 +3648,12 @@
         <v>14</v>
       </c>
       <c r="H20" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="14" t="s">
         <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="14" t="s">
-        <v>44</v>
       </c>
       <c r="B21" s="20" t="s">
         <v>17</v>
@@ -3612,16 +3666,22 @@
         <f>Tasks!I21</f>
         <v>46308</v>
       </c>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
+      <c r="E21" s="17">
+        <v>46304</v>
+      </c>
+      <c r="F21" s="17">
+        <v>46304</v>
+      </c>
       <c r="G21" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="14" t="s">
         <v>45</v>
-      </c>
-      <c r="H21" s="19"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="14" t="s">
-        <v>46</v>
       </c>
       <c r="B22" s="20" t="s">
         <v>17</v>
@@ -3634,16 +3694,20 @@
         <f>Tasks!I22</f>
         <v>46318</v>
       </c>
-      <c r="E22" s="17"/>
+      <c r="E22" s="17">
+        <v>46311</v>
+      </c>
       <c r="F22" s="17"/>
       <c r="G22" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="H22" s="19"/>
+        <v>46</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B23" s="20" t="s">
         <v>17</v>
@@ -3656,16 +3720,20 @@
         <f>Tasks!I23</f>
         <v>46315</v>
       </c>
-      <c r="E23" s="17"/>
+      <c r="E23" s="17">
+        <v>46315</v>
+      </c>
       <c r="F23" s="17"/>
       <c r="G23" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="H23" s="19"/>
+        <v>46</v>
+      </c>
+      <c r="H23" s="19" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B24" s="20" t="s">
         <v>17</v>
@@ -3681,13 +3749,13 @@
       <c r="E24" s="17"/>
       <c r="F24" s="17"/>
       <c r="G24" s="18" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H24" s="19"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="27" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B25" s="28"/>
       <c r="C25" s="28"/>
@@ -3697,12 +3765,12 @@
       <c r="G25" s="28"/>
       <c r="H25" s="28"/>
     </row>
-    <row r="26" spans="1:8" ht="42" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="14" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B26" s="25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C26" s="16">
         <f>Tasks!H26</f>
@@ -3712,16 +3780,20 @@
         <f>Tasks!I26</f>
         <v>46308</v>
       </c>
-      <c r="E26" s="17"/>
+      <c r="E26" s="17">
+        <v>46314</v>
+      </c>
       <c r="F26" s="17"/>
       <c r="G26" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="H26" s="19"/>
-    </row>
-    <row r="27" spans="1:8" ht="28" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+      <c r="H26" s="19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="14" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B27" s="15" t="s">
         <v>13</v>
@@ -3734,16 +3806,20 @@
         <f>Tasks!I27</f>
         <v>46308</v>
       </c>
-      <c r="E27" s="17"/>
+      <c r="E27" s="17">
+        <v>46314</v>
+      </c>
       <c r="F27" s="17"/>
       <c r="G27" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="H27" s="19"/>
-    </row>
-    <row r="28" spans="1:8" ht="28" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+      <c r="H27" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="14" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B28" s="15" t="s">
         <v>13</v>
@@ -3759,13 +3835,15 @@
       <c r="E28" s="17"/>
       <c r="F28" s="17"/>
       <c r="G28" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="H28" s="19"/>
-    </row>
-    <row r="29" spans="1:8" ht="28" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="H28" s="19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="14" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B29" s="22" t="s">
         <v>23</v>
@@ -3781,13 +3859,15 @@
       <c r="E29" s="17"/>
       <c r="F29" s="17"/>
       <c r="G29" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="H29" s="19"/>
-    </row>
-    <row r="30" spans="1:8" ht="28" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="H29" s="19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="14" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B30" s="15" t="s">
         <v>13</v>
@@ -3800,19 +3880,23 @@
         <f>Tasks!I30</f>
         <v>46309</v>
       </c>
-      <c r="E30" s="17"/>
+      <c r="E30" s="17">
+        <v>46314</v>
+      </c>
       <c r="F30" s="17"/>
       <c r="G30" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="H30" s="19"/>
-    </row>
-    <row r="31" spans="1:8" ht="28" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+      <c r="H30" s="19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="14" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="B31" s="26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31" s="16">
         <f>Tasks!H31</f>
@@ -3825,13 +3909,15 @@
       <c r="E31" s="17"/>
       <c r="F31" s="17"/>
       <c r="G31" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="H31" s="19"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="H31" s="19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="14" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="B32" s="15" t="s">
         <v>13</v>
@@ -3847,13 +3933,15 @@
       <c r="E32" s="17"/>
       <c r="F32" s="17"/>
       <c r="G32" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="H32" s="19"/>
-    </row>
-    <row r="33" spans="1:8" ht="28" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="H32" s="19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="14" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B33" s="20" t="s">
         <v>17</v>
@@ -3869,13 +3957,15 @@
       <c r="E33" s="17"/>
       <c r="F33" s="17"/>
       <c r="G33" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="H33" s="19"/>
+        <v>58</v>
+      </c>
+      <c r="H33" s="19" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="29" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="B34" s="30"/>
       <c r="C34" s="30"/>
@@ -3885,12 +3975,12 @@
       <c r="G34" s="30"/>
       <c r="H34" s="30"/>
     </row>
-    <row r="35" spans="1:8" ht="28" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="14" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B35" s="25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C35" s="16">
         <f>Tasks!H35</f>
@@ -3900,19 +3990,23 @@
         <f>Tasks!I35</f>
         <v>46310</v>
       </c>
-      <c r="E35" s="17"/>
+      <c r="E35" s="17">
+        <v>46314</v>
+      </c>
       <c r="F35" s="17"/>
       <c r="G35" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="H35" s="19"/>
-    </row>
-    <row r="36" spans="1:8" ht="28" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+      <c r="H35" s="19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="14" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B36" s="25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C36" s="16">
         <f>Tasks!H36</f>
@@ -3925,16 +4019,18 @@
       <c r="E36" s="17"/>
       <c r="F36" s="17"/>
       <c r="G36" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="H36" s="19"/>
-    </row>
-    <row r="37" spans="1:8" ht="28" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="H36" s="19" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="14" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37" s="16">
         <f>Tasks!H37</f>
@@ -3947,16 +4043,18 @@
       <c r="E37" s="17"/>
       <c r="F37" s="17"/>
       <c r="G37" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="H37" s="19"/>
-    </row>
-    <row r="38" spans="1:8" ht="28" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="H37" s="19" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="14" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="B38" s="26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C38" s="16">
         <f>Tasks!H38</f>
@@ -3969,16 +4067,18 @@
       <c r="E38" s="17"/>
       <c r="F38" s="17"/>
       <c r="G38" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="H38" s="19"/>
-    </row>
-    <row r="39" spans="1:8" ht="28" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="H38" s="19" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="14" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C39" s="16">
         <f>Tasks!H39</f>
@@ -3991,13 +4091,13 @@
       <c r="E39" s="17"/>
       <c r="F39" s="17"/>
       <c r="G39" s="18" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H39" s="19"/>
     </row>
-    <row r="40" spans="1:8" ht="28" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="14" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="B40" s="22" t="s">
         <v>23</v>
@@ -4013,13 +4113,15 @@
       <c r="E40" s="17"/>
       <c r="F40" s="17"/>
       <c r="G40" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="H40" s="19"/>
-    </row>
-    <row r="41" spans="1:8" ht="28" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+      <c r="H40" s="19" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="14" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="B41" s="22" t="s">
         <v>23</v>
@@ -4035,13 +4137,13 @@
       <c r="E41" s="17"/>
       <c r="F41" s="17"/>
       <c r="G41" s="18" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H41" s="19"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="14" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="B42" s="20" t="s">
         <v>17</v>
@@ -4057,13 +4159,13 @@
       <c r="E42" s="17"/>
       <c r="F42" s="17"/>
       <c r="G42" s="18" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H42" s="19"/>
     </row>
-    <row r="43" spans="1:8" ht="42" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="14" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="B43" s="15" t="s">
         <v>13</v>
@@ -4079,13 +4181,13 @@
       <c r="E43" s="17"/>
       <c r="F43" s="17"/>
       <c r="G43" s="18" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H43" s="19"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="31" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="B44" s="32"/>
       <c r="C44" s="32"/>
@@ -4097,7 +4199,7 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="14" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="B45" s="22" t="s">
         <v>23</v>
@@ -4113,13 +4215,13 @@
       <c r="E45" s="17"/>
       <c r="F45" s="17"/>
       <c r="G45" s="18" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H45" s="19"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="14" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="B46" s="15" t="s">
         <v>13</v>
@@ -4135,16 +4237,16 @@
       <c r="E46" s="17"/>
       <c r="F46" s="17"/>
       <c r="G46" s="18" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H46" s="19"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="14" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="B47" s="25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C47" s="16">
         <f>Tasks!H47</f>
@@ -4157,16 +4259,16 @@
       <c r="E47" s="17"/>
       <c r="F47" s="17"/>
       <c r="G47" s="18" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H47" s="19"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="14" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="B48" s="26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C48" s="16">
         <f>Tasks!H48</f>
@@ -4179,13 +4281,13 @@
       <c r="E48" s="17"/>
       <c r="F48" s="17"/>
       <c r="G48" s="18" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H48" s="19"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="14" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="B49" s="20" t="s">
         <v>17</v>
@@ -4201,13 +4303,13 @@
       <c r="E49" s="17"/>
       <c r="F49" s="17"/>
       <c r="G49" s="18" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H49" s="19"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="14" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="B50" s="22" t="s">
         <v>23</v>
@@ -4223,16 +4325,16 @@
       <c r="E50" s="17"/>
       <c r="F50" s="17"/>
       <c r="G50" s="18" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H50" s="19"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="14" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="B51" s="25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C51" s="16">
         <f>Tasks!H51</f>
@@ -4245,13 +4347,13 @@
       <c r="E51" s="17"/>
       <c r="F51" s="17"/>
       <c r="G51" s="18" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H51" s="19"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="14" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="B52" s="15" t="s">
         <v>13</v>
@@ -4267,13 +4369,13 @@
       <c r="E52" s="17"/>
       <c r="F52" s="17"/>
       <c r="G52" s="18" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H52" s="19"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="14" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="B53" s="22" t="s">
         <v>23</v>
@@ -4289,13 +4391,13 @@
       <c r="E53" s="17"/>
       <c r="F53" s="17"/>
       <c r="G53" s="18" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H53" s="19"/>
     </row>
-    <row r="54" spans="1:8" ht="28" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="14" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="B54" s="22" t="s">
         <v>23</v>
@@ -4311,13 +4413,13 @@
       <c r="E54" s="17"/>
       <c r="F54" s="17"/>
       <c r="G54" s="18" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H54" s="19"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="14" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="B55" s="15" t="s">
         <v>13</v>
@@ -4333,13 +4435,13 @@
       <c r="E55" s="17"/>
       <c r="F55" s="17"/>
       <c r="G55" s="18" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H55" s="19"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="14" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="B56" s="20" t="s">
         <v>17</v>
@@ -4355,16 +4457,16 @@
       <c r="E56" s="17"/>
       <c r="F56" s="17"/>
       <c r="G56" s="18" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H56" s="19"/>
     </row>
-    <row r="57" spans="1:8" ht="28" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="14" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="B57" s="25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C57" s="16">
         <f>Tasks!H57</f>
@@ -4377,16 +4479,16 @@
       <c r="E57" s="17"/>
       <c r="F57" s="17"/>
       <c r="G57" s="18" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H57" s="19"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="14" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="B58" s="26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C58" s="16">
         <f>Tasks!H58</f>
@@ -4399,13 +4501,13 @@
       <c r="E58" s="17"/>
       <c r="F58" s="17"/>
       <c r="G58" s="18" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H58" s="19"/>
     </row>
-    <row r="59" spans="1:8" ht="28" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="14" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="B59" s="15" t="s">
         <v>13</v>
@@ -4421,16 +4523,16 @@
       <c r="E59" s="17"/>
       <c r="F59" s="17"/>
       <c r="G59" s="18" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H59" s="19"/>
     </row>
-    <row r="60" spans="1:8" ht="28" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="14" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="B60" s="25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C60" s="16">
         <f>Tasks!H60</f>
@@ -4443,21 +4545,21 @@
       <c r="E60" s="17"/>
       <c r="F60" s="17"/>
       <c r="G60" s="18" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H60" s="19"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="33" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="34" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="B63" s="35" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
@@ -4465,44 +4567,44 @@
         <v>14</v>
       </c>
       <c r="B64" s="35" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" s="37" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="B65" s="35" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" s="38" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B66" s="35" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" s="39" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="B67" s="35" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" s="40" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B68" s="35" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" s="10" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -4571,109 +4673,109 @@
     <col min="50" max="50" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:50" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="41" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.2">
-      <c r="N3" s="80">
+      <c r="N3" s="81">
         <v>46279</v>
       </c>
-      <c r="O3" s="81"/>
-      <c r="P3" s="80">
+      <c r="O3" s="82"/>
+      <c r="P3" s="81">
         <v>46286</v>
       </c>
-      <c r="Q3" s="81"/>
-      <c r="R3" s="81"/>
-      <c r="S3" s="81"/>
-      <c r="T3" s="81"/>
-      <c r="U3" s="80">
+      <c r="Q3" s="82"/>
+      <c r="R3" s="82"/>
+      <c r="S3" s="82"/>
+      <c r="T3" s="82"/>
+      <c r="U3" s="81">
         <v>46293</v>
       </c>
-      <c r="V3" s="81"/>
-      <c r="W3" s="81"/>
-      <c r="X3" s="81"/>
-      <c r="Y3" s="81"/>
-      <c r="Z3" s="80">
+      <c r="V3" s="82"/>
+      <c r="W3" s="82"/>
+      <c r="X3" s="82"/>
+      <c r="Y3" s="82"/>
+      <c r="Z3" s="81">
         <v>46300</v>
       </c>
-      <c r="AA3" s="81"/>
-      <c r="AB3" s="81"/>
-      <c r="AC3" s="81"/>
-      <c r="AD3" s="81"/>
-      <c r="AE3" s="80">
+      <c r="AA3" s="82"/>
+      <c r="AB3" s="82"/>
+      <c r="AC3" s="82"/>
+      <c r="AD3" s="82"/>
+      <c r="AE3" s="81">
         <v>46307</v>
       </c>
-      <c r="AF3" s="81"/>
-      <c r="AG3" s="81"/>
-      <c r="AH3" s="81"/>
-      <c r="AI3" s="81"/>
-      <c r="AJ3" s="80">
+      <c r="AF3" s="82"/>
+      <c r="AG3" s="82"/>
+      <c r="AH3" s="82"/>
+      <c r="AI3" s="82"/>
+      <c r="AJ3" s="81">
         <v>46314</v>
       </c>
-      <c r="AK3" s="81"/>
-      <c r="AL3" s="81"/>
-      <c r="AM3" s="81"/>
-      <c r="AN3" s="81"/>
-      <c r="AO3" s="80">
+      <c r="AK3" s="82"/>
+      <c r="AL3" s="82"/>
+      <c r="AM3" s="82"/>
+      <c r="AN3" s="82"/>
+      <c r="AO3" s="81">
         <v>46321</v>
       </c>
-      <c r="AP3" s="81"/>
-      <c r="AQ3" s="81"/>
-      <c r="AR3" s="81"/>
-      <c r="AS3" s="81"/>
-      <c r="AT3" s="80">
+      <c r="AP3" s="82"/>
+      <c r="AQ3" s="82"/>
+      <c r="AR3" s="82"/>
+      <c r="AS3" s="82"/>
+      <c r="AT3" s="81">
         <v>46328</v>
       </c>
-      <c r="AU3" s="81"/>
-      <c r="AV3" s="81"/>
-      <c r="AW3" s="81"/>
+      <c r="AU3" s="82"/>
+      <c r="AV3" s="82"/>
+      <c r="AW3" s="82"/>
     </row>
     <row r="4" spans="1:50" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="L4" s="11" t="s">
         <v>9</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="N4" s="42">
         <v>46282</v>
@@ -4784,15 +4886,15 @@
         <v>46331</v>
       </c>
       <c r="AX4" s="11" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="C5" s="13" t="s">
         <v>11</v>
@@ -4855,13 +4957,13 @@
     </row>
     <row r="6" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A6" s="45" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="B6" s="45" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="D6" s="46" t="s">
         <v>13</v>
@@ -5041,18 +5143,18 @@
         <v/>
       </c>
       <c r="AX6" s="49" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A7" s="45" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="B7" s="45" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="D7" s="50" t="s">
         <v>17</v>
@@ -5232,18 +5334,18 @@
         <v/>
       </c>
       <c r="AX7" s="49" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A8" s="45" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="B8" s="45" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="C8" s="45" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="D8" s="51" t="s">
         <v>19</v>
@@ -5423,18 +5525,18 @@
         <v/>
       </c>
       <c r="AX8" s="49" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A9" s="45" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="B9" s="45" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="C9" s="45" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="D9" s="51" t="s">
         <v>19</v>
@@ -5614,18 +5716,18 @@
         <v/>
       </c>
       <c r="AX9" s="49" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A10" s="45" t="s">
+        <v>156</v>
+      </c>
+      <c r="B10" s="45" t="s">
         <v>143</v>
       </c>
-      <c r="B10" s="45" t="s">
-        <v>130</v>
-      </c>
       <c r="C10" s="45" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="D10" s="52" t="s">
         <v>23</v>
@@ -5805,18 +5907,18 @@
         <v/>
       </c>
       <c r="AX10" s="49" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A11" s="45" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="B11" s="45" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="C11" s="45" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="D11" s="51" t="s">
         <v>19</v>
@@ -5996,18 +6098,18 @@
         <v/>
       </c>
       <c r="AX11" s="49" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A12" s="45" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="B12" s="45" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="C12" s="45" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="D12" s="51" t="s">
         <v>19</v>
@@ -6187,18 +6289,18 @@
         <v/>
       </c>
       <c r="AX12" s="49" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A13" s="45" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="B13" s="45" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="C13" s="45" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="D13" s="50" t="s">
         <v>17</v>
@@ -6378,18 +6480,18 @@
         <v/>
       </c>
       <c r="AX13" s="49" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A14" s="45" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="B14" s="45" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="C14" s="45" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="D14" s="51" t="s">
         <v>19</v>
@@ -6569,15 +6671,15 @@
         <v/>
       </c>
       <c r="AX14" s="49" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A15" s="23" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="C15" s="24" t="s">
         <v>30</v>
@@ -6640,13 +6742,13 @@
     </row>
     <row r="16" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A16" s="45" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="B16" s="45" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="C16" s="45" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="D16" s="50" t="s">
         <v>17</v>
@@ -6826,18 +6928,18 @@
         <v/>
       </c>
       <c r="AX16" s="49" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A17" s="45" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="B17" s="45" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="C17" s="45" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="D17" s="52" t="s">
         <v>23</v>
@@ -6849,7 +6951,7 @@
         <v>1</v>
       </c>
       <c r="G17" s="45" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="H17" s="47">
         <v>46304</v>
@@ -6862,17 +6964,17 @@
         <f>IF('Project Status'!E17="","",'Project Status'!E17)</f>
         <v>46303</v>
       </c>
-      <c r="K17" s="47" t="str">
+      <c r="K17" s="47">
         <f>IF('Project Status'!F17="","",'Project Status'!F17)</f>
-        <v/>
+        <v>46304</v>
       </c>
       <c r="L17" s="45" t="str">
         <f>IF('Project Status'!G17="","",'Project Status'!G17)</f>
-        <v>In progress</v>
-      </c>
-      <c r="M17" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="M17" s="45">
         <f>IF(OR(K17="",I17=""),"",IF(K17&gt;=I17,NETWORKDAYS(I17,K17,Holidays!$A$2:$A$40)-1,-(NETWORKDAYS(K17,I17,Holidays!$A$2:$A$40)-1)))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N17" s="48" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -7019,21 +7121,21 @@
         <v/>
       </c>
       <c r="AX17" s="49" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A18" s="45" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="B18" s="45" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="C18" s="45" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="D18" s="54" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E18" s="45">
         <v>1</v>
@@ -7042,7 +7144,7 @@
         <v>1</v>
       </c>
       <c r="G18" s="45" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="H18" s="47">
         <v>46304</v>
@@ -7212,21 +7314,21 @@
         <v/>
       </c>
       <c r="AX18" s="49" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A19" s="45" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="B19" s="45" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="C19" s="45" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="D19" s="55" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E19" s="45">
         <v>1</v>
@@ -7235,7 +7337,7 @@
         <v>1</v>
       </c>
       <c r="G19" s="45" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="H19" s="47">
         <v>46304</v>
@@ -7405,18 +7507,18 @@
         <v/>
       </c>
       <c r="AX19" s="49" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A20" s="45" t="s">
+        <v>182</v>
+      </c>
+      <c r="B20" s="45" t="s">
         <v>169</v>
       </c>
-      <c r="B20" s="45" t="s">
-        <v>156</v>
-      </c>
       <c r="C20" s="45" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="D20" s="46" t="s">
         <v>13</v>
@@ -7428,7 +7530,7 @@
         <v>1</v>
       </c>
       <c r="G20" s="45" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="H20" s="47">
         <v>46304</v>
@@ -7598,18 +7700,18 @@
         <v/>
       </c>
       <c r="AX20" s="49" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
     </row>
     <row r="21" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A21" s="45" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="B21" s="45" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="C21" s="45" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="D21" s="50" t="s">
         <v>17</v>
@@ -7621,7 +7723,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="45" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="H21" s="47">
         <v>46308</v>
@@ -7630,21 +7732,21 @@
         <f>WORKDAY(H21,E21-1,Holidays!$A$2:$A$40)</f>
         <v>46308</v>
       </c>
-      <c r="J21" s="47" t="str">
+      <c r="J21" s="47">
         <f>IF('Project Status'!E21="","",'Project Status'!E21)</f>
-        <v/>
-      </c>
-      <c r="K21" s="47" t="str">
+        <v>46304</v>
+      </c>
+      <c r="K21" s="47">
         <f>IF('Project Status'!F21="","",'Project Status'!F21)</f>
-        <v/>
+        <v>46304</v>
       </c>
       <c r="L21" s="45" t="str">
         <f>IF('Project Status'!G21="","",'Project Status'!G21)</f>
-        <v>Pending</v>
-      </c>
-      <c r="M21" s="45" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="M21" s="45">
         <f>IF(OR(K21="",I21=""),"",IF(K21&gt;=I21,NETWORKDAYS(I21,K21,Holidays!$A$2:$A$40)-1,-(NETWORKDAYS(K21,I21,Holidays!$A$2:$A$40)-1)))</f>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="N21" s="48" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -7712,7 +7814,7 @@
       </c>
       <c r="AD21" s="48" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v/>
+        <v>●</v>
       </c>
       <c r="AE21" s="48" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7791,18 +7893,18 @@
         <v/>
       </c>
       <c r="AX21" s="49" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A22" s="45" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="B22" s="45" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="C22" s="45" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="D22" s="50" t="s">
         <v>17</v>
@@ -7814,7 +7916,7 @@
         <v>2</v>
       </c>
       <c r="G22" s="45" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="H22" s="47">
         <v>46311</v>
@@ -7823,9 +7925,9 @@
         <f>WORKDAY(H22,E22-1,Holidays!$A$2:$A$40)</f>
         <v>46318</v>
       </c>
-      <c r="J22" s="47" t="str">
+      <c r="J22" s="47">
         <f>IF('Project Status'!E22="","",'Project Status'!E22)</f>
-        <v/>
+        <v>46311</v>
       </c>
       <c r="K22" s="47" t="str">
         <f>IF('Project Status'!F22="","",'Project Status'!F22)</f>
@@ -7833,7 +7935,7 @@
       </c>
       <c r="L22" s="45" t="str">
         <f>IF('Project Status'!G22="","",'Project Status'!G22)</f>
-        <v>Pending</v>
+        <v>In progress</v>
       </c>
       <c r="M22" s="45" t="str">
         <f>IF(OR(K22="",I22=""),"",IF(K22&gt;=I22,NETWORKDAYS(I22,K22,Holidays!$A$2:$A$40)-1,-(NETWORKDAYS(K22,I22,Holidays!$A$2:$A$40)-1)))</f>
@@ -7925,15 +8027,15 @@
       </c>
       <c r="AI22" s="48" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v/>
+        <v>●</v>
       </c>
       <c r="AJ22" s="48" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v/>
+        <v>●</v>
       </c>
       <c r="AK22" s="48" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v/>
+        <v>●</v>
       </c>
       <c r="AL22" s="48" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -7984,18 +8086,18 @@
         <v/>
       </c>
       <c r="AX22" s="49" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
     </row>
     <row r="23" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A23" s="45" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="D23" s="50" t="s">
         <v>17</v>
@@ -8007,7 +8109,7 @@
         <v>1</v>
       </c>
       <c r="G23" s="45" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="H23" s="47">
         <v>46315</v>
@@ -8016,9 +8118,9 @@
         <f>WORKDAY(H23,E23-1,Holidays!$A$2:$A$40)</f>
         <v>46315</v>
       </c>
-      <c r="J23" s="47" t="str">
+      <c r="J23" s="47">
         <f>IF('Project Status'!E23="","",'Project Status'!E23)</f>
-        <v/>
+        <v>46315</v>
       </c>
       <c r="K23" s="47" t="str">
         <f>IF('Project Status'!F23="","",'Project Status'!F23)</f>
@@ -8026,7 +8128,7 @@
       </c>
       <c r="L23" s="45" t="str">
         <f>IF('Project Status'!G23="","",'Project Status'!G23)</f>
-        <v>Pending</v>
+        <v>In progress</v>
       </c>
       <c r="M23" s="45" t="str">
         <f>IF(OR(K23="",I23=""),"",IF(K23&gt;=I23,NETWORKDAYS(I23,K23,Holidays!$A$2:$A$40)-1,-(NETWORKDAYS(K23,I23,Holidays!$A$2:$A$40)-1)))</f>
@@ -8126,7 +8228,7 @@
       </c>
       <c r="AK23" s="48" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v/>
+        <v>●</v>
       </c>
       <c r="AL23" s="48" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -8177,18 +8279,18 @@
         <v/>
       </c>
       <c r="AX23" s="49" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
     </row>
     <row r="24" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A24" s="45" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="B24" s="45" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="C24" s="45" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="D24" s="50" t="s">
         <v>17</v>
@@ -8200,7 +8302,7 @@
         <v>1</v>
       </c>
       <c r="G24" s="45" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="H24" s="47">
         <v>46322</v>
@@ -8370,18 +8472,18 @@
         <v/>
       </c>
       <c r="AX24" s="49" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
     </row>
     <row r="25" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A25" s="27" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="B25" s="28" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D25" s="28"/>
       <c r="E25" s="28">
@@ -8441,16 +8543,16 @@
     </row>
     <row r="26" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A26" s="45" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="B26" s="45" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="C26" s="45" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="D26" s="54" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E26" s="45">
         <v>1</v>
@@ -8459,7 +8561,7 @@
         <v>1</v>
       </c>
       <c r="G26" s="45" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="H26" s="47">
         <v>46308</v>
@@ -8468,9 +8570,9 @@
         <f>WORKDAY(H26,E26-1,Holidays!$A$2:$A$40)</f>
         <v>46308</v>
       </c>
-      <c r="J26" s="47" t="str">
+      <c r="J26" s="47">
         <f>IF('Project Status'!E26="","",'Project Status'!E26)</f>
-        <v/>
+        <v>46314</v>
       </c>
       <c r="K26" s="47" t="str">
         <f>IF('Project Status'!F26="","",'Project Status'!F26)</f>
@@ -8478,7 +8580,7 @@
       </c>
       <c r="L26" s="45" t="str">
         <f>IF('Project Status'!G26="","",'Project Status'!G26)</f>
-        <v>Pending</v>
+        <v>In progress</v>
       </c>
       <c r="M26" s="45" t="str">
         <f>IF(OR(K26="",I26=""),"",IF(K26&gt;=I26,NETWORKDAYS(I26,K26,Holidays!$A$2:$A$40)-1,-(NETWORKDAYS(K26,I26,Holidays!$A$2:$A$40)-1)))</f>
@@ -8574,11 +8676,11 @@
       </c>
       <c r="AJ26" s="48" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v/>
+        <v>●</v>
       </c>
       <c r="AK26" s="48" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v/>
+        <v>●</v>
       </c>
       <c r="AL26" s="48" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -8629,18 +8731,18 @@
         <v/>
       </c>
       <c r="AX26" s="49" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
     </row>
     <row r="27" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A27" s="45" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="B27" s="45" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="C27" s="45" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="D27" s="46" t="s">
         <v>13</v>
@@ -8652,7 +8754,7 @@
         <v>1</v>
       </c>
       <c r="G27" s="45" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="H27" s="47">
         <v>46308</v>
@@ -8661,9 +8763,9 @@
         <f>WORKDAY(H27,E27-1,Holidays!$A$2:$A$40)</f>
         <v>46308</v>
       </c>
-      <c r="J27" s="47" t="str">
+      <c r="J27" s="47">
         <f>IF('Project Status'!E27="","",'Project Status'!E27)</f>
-        <v/>
+        <v>46314</v>
       </c>
       <c r="K27" s="47" t="str">
         <f>IF('Project Status'!F27="","",'Project Status'!F27)</f>
@@ -8671,7 +8773,7 @@
       </c>
       <c r="L27" s="45" t="str">
         <f>IF('Project Status'!G27="","",'Project Status'!G27)</f>
-        <v>Pending</v>
+        <v>In progress</v>
       </c>
       <c r="M27" s="45" t="str">
         <f>IF(OR(K27="",I27=""),"",IF(K27&gt;=I27,NETWORKDAYS(I27,K27,Holidays!$A$2:$A$40)-1,-(NETWORKDAYS(K27,I27,Holidays!$A$2:$A$40)-1)))</f>
@@ -8767,11 +8869,11 @@
       </c>
       <c r="AJ27" s="48" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v/>
+        <v>●</v>
       </c>
       <c r="AK27" s="48" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v/>
+        <v>●</v>
       </c>
       <c r="AL27" s="48" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -8822,18 +8924,18 @@
         <v/>
       </c>
       <c r="AX27" s="49" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
     </row>
     <row r="28" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A28" s="45" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="B28" s="45" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="C28" s="45" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="D28" s="46" t="s">
         <v>13</v>
@@ -8845,7 +8947,7 @@
         <v>2</v>
       </c>
       <c r="G28" s="45" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="H28" s="47">
         <v>46310</v>
@@ -8864,7 +8966,7 @@
       </c>
       <c r="L28" s="45" t="str">
         <f>IF('Project Status'!G28="","",'Project Status'!G28)</f>
-        <v>Pending</v>
+        <v>Incident</v>
       </c>
       <c r="M28" s="45" t="str">
         <f>IF(OR(K28="",I28=""),"",IF(K28&gt;=I28,NETWORKDAYS(I28,K28,Holidays!$A$2:$A$40)-1,-(NETWORKDAYS(K28,I28,Holidays!$A$2:$A$40)-1)))</f>
@@ -9015,18 +9117,18 @@
         <v/>
       </c>
       <c r="AX28" s="49" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
     </row>
     <row r="29" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A29" s="45" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="B29" s="45" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="C29" s="45" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="D29" s="52" t="s">
         <v>23</v>
@@ -9038,7 +9140,7 @@
         <v>3</v>
       </c>
       <c r="G29" s="45" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="H29" s="47">
         <v>46308</v>
@@ -9057,7 +9159,7 @@
       </c>
       <c r="L29" s="45" t="str">
         <f>IF('Project Status'!G29="","",'Project Status'!G29)</f>
-        <v>Pending</v>
+        <v>Incident</v>
       </c>
       <c r="M29" s="45" t="str">
         <f>IF(OR(K29="",I29=""),"",IF(K29&gt;=I29,NETWORKDAYS(I29,K29,Holidays!$A$2:$A$40)-1,-(NETWORKDAYS(K29,I29,Holidays!$A$2:$A$40)-1)))</f>
@@ -9208,18 +9310,18 @@
         <v/>
       </c>
       <c r="AX29" s="49" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
     </row>
     <row r="30" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A30" s="45" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="B30" s="45" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="C30" s="45" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="D30" s="46" t="s">
         <v>13</v>
@@ -9231,7 +9333,7 @@
         <v>1</v>
       </c>
       <c r="G30" s="45" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="H30" s="47">
         <v>46309</v>
@@ -9240,9 +9342,9 @@
         <f>WORKDAY(H30,E30-1,Holidays!$A$2:$A$40)</f>
         <v>46309</v>
       </c>
-      <c r="J30" s="47" t="str">
+      <c r="J30" s="47">
         <f>IF('Project Status'!E30="","",'Project Status'!E30)</f>
-        <v/>
+        <v>46314</v>
       </c>
       <c r="K30" s="47" t="str">
         <f>IF('Project Status'!F30="","",'Project Status'!F30)</f>
@@ -9250,7 +9352,7 @@
       </c>
       <c r="L30" s="45" t="str">
         <f>IF('Project Status'!G30="","",'Project Status'!G30)</f>
-        <v>Pending</v>
+        <v>In progress</v>
       </c>
       <c r="M30" s="45" t="str">
         <f>IF(OR(K30="",I30=""),"",IF(K30&gt;=I30,NETWORKDAYS(I30,K30,Holidays!$A$2:$A$40)-1,-(NETWORKDAYS(K30,I30,Holidays!$A$2:$A$40)-1)))</f>
@@ -9346,11 +9448,11 @@
       </c>
       <c r="AJ30" s="48" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v/>
+        <v>●</v>
       </c>
       <c r="AK30" s="48" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v/>
+        <v>●</v>
       </c>
       <c r="AL30" s="48" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -9401,21 +9503,21 @@
         <v/>
       </c>
       <c r="AX30" s="49" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
     </row>
     <row r="31" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A31" s="45" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="B31" s="45" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="C31" s="45" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="D31" s="55" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E31" s="45">
         <v>1</v>
@@ -9424,7 +9526,7 @@
         <v>1</v>
       </c>
       <c r="G31" s="45" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="H31" s="47">
         <v>46308</v>
@@ -9443,7 +9545,7 @@
       </c>
       <c r="L31" s="45" t="str">
         <f>IF('Project Status'!G31="","",'Project Status'!G31)</f>
-        <v>Pending</v>
+        <v>Incident</v>
       </c>
       <c r="M31" s="45" t="str">
         <f>IF(OR(K31="",I31=""),"",IF(K31&gt;=I31,NETWORKDAYS(I31,K31,Holidays!$A$2:$A$40)-1,-(NETWORKDAYS(K31,I31,Holidays!$A$2:$A$40)-1)))</f>
@@ -9594,18 +9696,18 @@
         <v/>
       </c>
       <c r="AX31" s="49" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
     </row>
     <row r="32" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A32" s="45" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="B32" s="45" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="C32" s="45" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="D32" s="46" t="s">
         <v>13</v>
@@ -9617,7 +9719,7 @@
         <v>1</v>
       </c>
       <c r="G32" s="45" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="H32" s="47">
         <v>46314</v>
@@ -9636,7 +9738,7 @@
       </c>
       <c r="L32" s="45" t="str">
         <f>IF('Project Status'!G32="","",'Project Status'!G32)</f>
-        <v>Pending</v>
+        <v>Incident</v>
       </c>
       <c r="M32" s="45" t="str">
         <f>IF(OR(K32="",I32=""),"",IF(K32&gt;=I32,NETWORKDAYS(I32,K32,Holidays!$A$2:$A$40)-1,-(NETWORKDAYS(K32,I32,Holidays!$A$2:$A$40)-1)))</f>
@@ -9787,18 +9889,18 @@
         <v/>
       </c>
       <c r="AX32" s="49" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
     </row>
     <row r="33" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A33" s="45" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="B33" s="45" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="C33" s="45" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="D33" s="50" t="s">
         <v>17</v>
@@ -9810,7 +9912,7 @@
         <v>1</v>
       </c>
       <c r="G33" s="45" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="H33" s="47">
         <v>46309</v>
@@ -9829,7 +9931,7 @@
       </c>
       <c r="L33" s="45" t="str">
         <f>IF('Project Status'!G33="","",'Project Status'!G33)</f>
-        <v>Pending</v>
+        <v>Incident</v>
       </c>
       <c r="M33" s="45" t="str">
         <f>IF(OR(K33="",I33=""),"",IF(K33&gt;=I33,NETWORKDAYS(I33,K33,Holidays!$A$2:$A$40)-1,-(NETWORKDAYS(K33,I33,Holidays!$A$2:$A$40)-1)))</f>
@@ -9980,18 +10082,18 @@
         <v/>
       </c>
       <c r="AX33" s="49" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
     </row>
     <row r="34" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A34" s="29" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="B34" s="30" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="C34" s="30" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D34" s="30"/>
       <c r="E34" s="30">
@@ -10051,16 +10153,16 @@
     </row>
     <row r="35" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A35" s="45" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="B35" s="45" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="C35" s="45" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="D35" s="54" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E35" s="45">
         <v>1</v>
@@ -10069,7 +10171,7 @@
         <v>1</v>
       </c>
       <c r="G35" s="45" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="H35" s="47">
         <v>46310</v>
@@ -10078,9 +10180,9 @@
         <f>WORKDAY(H35,E35-1,Holidays!$A$2:$A$40)</f>
         <v>46310</v>
       </c>
-      <c r="J35" s="47" t="str">
+      <c r="J35" s="47">
         <f>IF('Project Status'!E35="","",'Project Status'!E35)</f>
-        <v/>
+        <v>46314</v>
       </c>
       <c r="K35" s="47" t="str">
         <f>IF('Project Status'!F35="","",'Project Status'!F35)</f>
@@ -10088,7 +10190,7 @@
       </c>
       <c r="L35" s="45" t="str">
         <f>IF('Project Status'!G35="","",'Project Status'!G35)</f>
-        <v>Pending</v>
+        <v>In progress</v>
       </c>
       <c r="M35" s="45" t="str">
         <f>IF(OR(K35="",I35=""),"",IF(K35&gt;=I35,NETWORKDAYS(I35,K35,Holidays!$A$2:$A$40)-1,-(NETWORKDAYS(K35,I35,Holidays!$A$2:$A$40)-1)))</f>
@@ -10184,11 +10286,11 @@
       </c>
       <c r="AJ35" s="48" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v/>
+        <v>●</v>
       </c>
       <c r="AK35" s="48" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v/>
+        <v>●</v>
       </c>
       <c r="AL35" s="48" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -10239,21 +10341,21 @@
         <v/>
       </c>
       <c r="AX35" s="49" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
     </row>
     <row r="36" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A36" s="45" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="B36" s="45" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="C36" s="45" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="D36" s="54" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E36" s="45">
         <v>2</v>
@@ -10262,7 +10364,7 @@
         <v>2</v>
       </c>
       <c r="G36" s="45" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="H36" s="47">
         <v>46311</v>
@@ -10281,7 +10383,7 @@
       </c>
       <c r="L36" s="45" t="str">
         <f>IF('Project Status'!G36="","",'Project Status'!G36)</f>
-        <v>Pending</v>
+        <v>Incident</v>
       </c>
       <c r="M36" s="45" t="str">
         <f>IF(OR(K36="",I36=""),"",IF(K36&gt;=I36,NETWORKDAYS(I36,K36,Holidays!$A$2:$A$40)-1,-(NETWORKDAYS(K36,I36,Holidays!$A$2:$A$40)-1)))</f>
@@ -10432,21 +10534,21 @@
         <v/>
       </c>
       <c r="AX36" s="49" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
     </row>
     <row r="37" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A37" s="45" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="B37" s="45" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="C37" s="45" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="D37" s="55" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E37" s="45">
         <v>2</v>
@@ -10455,7 +10557,7 @@
         <v>2</v>
       </c>
       <c r="G37" s="45" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H37" s="47">
         <v>46309</v>
@@ -10474,7 +10576,7 @@
       </c>
       <c r="L37" s="45" t="str">
         <f>IF('Project Status'!G37="","",'Project Status'!G37)</f>
-        <v>Pending</v>
+        <v>Incident</v>
       </c>
       <c r="M37" s="45" t="str">
         <f>IF(OR(K37="",I37=""),"",IF(K37&gt;=I37,NETWORKDAYS(I37,K37,Holidays!$A$2:$A$40)-1,-(NETWORKDAYS(K37,I37,Holidays!$A$2:$A$40)-1)))</f>
@@ -10625,21 +10727,21 @@
         <v/>
       </c>
       <c r="AX37" s="49" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
     </row>
     <row r="38" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A38" s="45" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="B38" s="45" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="C38" s="45" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="D38" s="55" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E38" s="45">
         <v>2</v>
@@ -10648,7 +10750,7 @@
         <v>2</v>
       </c>
       <c r="G38" s="45" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="H38" s="47">
         <v>46311</v>
@@ -10667,7 +10769,7 @@
       </c>
       <c r="L38" s="45" t="str">
         <f>IF('Project Status'!G38="","",'Project Status'!G38)</f>
-        <v>Pending</v>
+        <v>Incident</v>
       </c>
       <c r="M38" s="45" t="str">
         <f>IF(OR(K38="",I38=""),"",IF(K38&gt;=I38,NETWORKDAYS(I38,K38,Holidays!$A$2:$A$40)-1,-(NETWORKDAYS(K38,I38,Holidays!$A$2:$A$40)-1)))</f>
@@ -10818,21 +10920,21 @@
         <v/>
       </c>
       <c r="AX38" s="49" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
     </row>
     <row r="39" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A39" s="45" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="B39" s="45" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="C39" s="45" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="D39" s="55" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E39" s="45">
         <v>1</v>
@@ -10841,7 +10943,7 @@
         <v>1</v>
       </c>
       <c r="G39" s="45" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="H39" s="47">
         <v>46315</v>
@@ -11011,18 +11113,18 @@
         <v/>
       </c>
       <c r="AX39" s="49" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
     </row>
     <row r="40" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A40" s="45" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="B40" s="45" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="C40" s="45" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="D40" s="52" t="s">
         <v>23</v>
@@ -11034,7 +11136,7 @@
         <v>1</v>
       </c>
       <c r="G40" s="45" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="H40" s="47">
         <v>46314</v>
@@ -11053,7 +11155,7 @@
       </c>
       <c r="L40" s="45" t="str">
         <f>IF('Project Status'!G40="","",'Project Status'!G40)</f>
-        <v>Pending</v>
+        <v>Incident</v>
       </c>
       <c r="M40" s="45" t="str">
         <f>IF(OR(K40="",I40=""),"",IF(K40&gt;=I40,NETWORKDAYS(I40,K40,Holidays!$A$2:$A$40)-1,-(NETWORKDAYS(K40,I40,Holidays!$A$2:$A$40)-1)))</f>
@@ -11204,18 +11306,18 @@
         <v/>
       </c>
       <c r="AX40" s="49" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
     </row>
     <row r="41" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A41" s="45" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B41" s="45" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="C41" s="45" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="D41" s="52" t="s">
         <v>23</v>
@@ -11227,7 +11329,7 @@
         <v>1</v>
       </c>
       <c r="G41" s="45" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="H41" s="47">
         <v>46315</v>
@@ -11397,18 +11499,18 @@
         <v/>
       </c>
       <c r="AX41" s="49" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
     </row>
     <row r="42" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A42" s="45" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="B42" s="45" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="C42" s="45" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="D42" s="50" t="s">
         <v>17</v>
@@ -11420,7 +11522,7 @@
         <v>1</v>
       </c>
       <c r="G42" s="45" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="H42" s="47">
         <v>46316</v>
@@ -11590,18 +11692,18 @@
         <v/>
       </c>
       <c r="AX42" s="49" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
     </row>
     <row r="43" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A43" s="45" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="B43" s="45" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="C43" s="45" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="D43" s="46" t="s">
         <v>13</v>
@@ -11613,7 +11715,7 @@
         <v>1</v>
       </c>
       <c r="G43" s="45" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="H43" s="47">
         <v>46315</v>
@@ -11783,18 +11885,18 @@
         <v/>
       </c>
       <c r="AX43" s="49" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
     </row>
     <row r="44" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A44" s="31" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="B44" s="32" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="C44" s="32" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="D44" s="32"/>
       <c r="E44" s="32">
@@ -11854,13 +11956,13 @@
     </row>
     <row r="45" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A45" s="45" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="B45" s="45" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="C45" s="45" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="D45" s="52" t="s">
         <v>23</v>
@@ -11872,7 +11974,7 @@
         <v>2</v>
       </c>
       <c r="G45" s="45" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="H45" s="47">
         <v>46316</v>
@@ -12042,18 +12144,18 @@
         <v/>
       </c>
       <c r="AX45" s="49" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
     </row>
     <row r="46" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A46" s="45" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="B46" s="45" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="C46" s="45" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="D46" s="46" t="s">
         <v>13</v>
@@ -12065,7 +12167,7 @@
         <v>2</v>
       </c>
       <c r="G46" s="45" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="H46" s="47">
         <v>46316</v>
@@ -12235,21 +12337,21 @@
         <v/>
       </c>
       <c r="AX46" s="49" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
     </row>
     <row r="47" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A47" s="45" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="B47" s="45" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="C47" s="45" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="D47" s="54" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E47" s="45">
         <v>2</v>
@@ -12258,7 +12360,7 @@
         <v>2</v>
       </c>
       <c r="G47" s="45" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="H47" s="47">
         <v>46315</v>
@@ -12428,21 +12530,21 @@
         <v/>
       </c>
       <c r="AX47" s="49" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
     </row>
     <row r="48" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A48" s="45" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="B48" s="45" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="C48" s="45" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="D48" s="55" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E48" s="45">
         <v>2</v>
@@ -12451,7 +12553,7 @@
         <v>2</v>
       </c>
       <c r="G48" s="45" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="H48" s="47">
         <v>46316</v>
@@ -12621,18 +12723,18 @@
         <v/>
       </c>
       <c r="AX48" s="49" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
     </row>
     <row r="49" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A49" s="45" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="B49" s="45" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="C49" s="45" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="D49" s="50" t="s">
         <v>17</v>
@@ -12644,7 +12746,7 @@
         <v>2</v>
       </c>
       <c r="G49" s="45" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="H49" s="47">
         <v>46317</v>
@@ -12814,18 +12916,18 @@
         <v/>
       </c>
       <c r="AX49" s="49" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
     </row>
     <row r="50" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A50" s="45" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="B50" s="45" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="C50" s="45" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="D50" s="52" t="s">
         <v>23</v>
@@ -12837,7 +12939,7 @@
         <v>1</v>
       </c>
       <c r="G50" s="45" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="H50" s="47">
         <v>46321</v>
@@ -13007,21 +13109,21 @@
         <v/>
       </c>
       <c r="AX50" s="49" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
     </row>
     <row r="51" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A51" s="45" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="B51" s="45" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="C51" s="45" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="D51" s="54" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E51" s="45">
         <v>1</v>
@@ -13030,7 +13132,7 @@
         <v>1</v>
       </c>
       <c r="G51" s="45" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="H51" s="47">
         <v>46322</v>
@@ -13200,18 +13302,18 @@
         <v/>
       </c>
       <c r="AX51" s="49" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="52" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A52" s="45" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="B52" s="45" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="C52" s="45" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="D52" s="46" t="s">
         <v>13</v>
@@ -13223,7 +13325,7 @@
         <v>1</v>
       </c>
       <c r="G52" s="45" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="H52" s="47">
         <v>46322</v>
@@ -13393,18 +13495,18 @@
         <v/>
       </c>
       <c r="AX52" s="49" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
     </row>
     <row r="53" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A53" s="45" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="B53" s="45" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="C53" s="45" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="D53" s="52" t="s">
         <v>23</v>
@@ -13416,7 +13518,7 @@
         <v>1</v>
       </c>
       <c r="G53" s="45" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="H53" s="47">
         <v>46323</v>
@@ -13586,18 +13688,18 @@
         <v/>
       </c>
       <c r="AX53" s="49" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
     </row>
     <row r="54" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A54" s="45" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="B54" s="45" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="C54" s="45" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="D54" s="52" t="s">
         <v>23</v>
@@ -13609,7 +13711,7 @@
         <v>1</v>
       </c>
       <c r="G54" s="45" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="H54" s="47">
         <v>46324</v>
@@ -13779,18 +13881,18 @@
         <v/>
       </c>
       <c r="AX54" s="49" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
     </row>
     <row r="55" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A55" s="45" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="B55" s="45" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="C55" s="45" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="D55" s="46" t="s">
         <v>13</v>
@@ -13802,7 +13904,7 @@
         <v>1</v>
       </c>
       <c r="G55" s="45" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="H55" s="47">
         <v>46324</v>
@@ -13972,18 +14074,18 @@
         <v/>
       </c>
       <c r="AX55" s="49" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
     </row>
     <row r="56" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A56" s="45" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="B56" s="45" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="C56" s="45" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="D56" s="50" t="s">
         <v>17</v>
@@ -13995,7 +14097,7 @@
         <v>1</v>
       </c>
       <c r="G56" s="45" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="H56" s="47">
         <v>46324</v>
@@ -14165,21 +14267,21 @@
         <v/>
       </c>
       <c r="AX56" s="49" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
     </row>
     <row r="57" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A57" s="45" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="B57" s="45" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="C57" s="45" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="D57" s="54" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E57" s="45">
         <v>1</v>
@@ -14188,7 +14290,7 @@
         <v>1</v>
       </c>
       <c r="G57" s="45" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="H57" s="47">
         <v>46324</v>
@@ -14358,21 +14460,21 @@
         <v/>
       </c>
       <c r="AX57" s="49" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
     </row>
     <row r="58" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A58" s="45" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="B58" s="45" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="C58" s="45" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="D58" s="55" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E58" s="45">
         <v>1</v>
@@ -14381,7 +14483,7 @@
         <v>1</v>
       </c>
       <c r="G58" s="45" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="H58" s="47">
         <v>46324</v>
@@ -14551,18 +14653,18 @@
         <v/>
       </c>
       <c r="AX58" s="49" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
     </row>
     <row r="59" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A59" s="45" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="B59" s="45" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="C59" s="45" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="D59" s="46" t="s">
         <v>13</v>
@@ -14574,7 +14676,7 @@
         <v>1</v>
       </c>
       <c r="G59" s="45" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="H59" s="47">
         <v>46325</v>
@@ -14744,21 +14846,21 @@
         <v/>
       </c>
       <c r="AX59" s="49" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
     </row>
     <row r="60" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A60" s="45" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="B60" s="45" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="C60" s="45" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="D60" s="54" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E60" s="45">
         <v>2</v>
@@ -14767,7 +14869,7 @@
         <v>2</v>
       </c>
       <c r="G60" s="45" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="H60" s="47">
         <v>46328</v>
@@ -14937,84 +15039,84 @@
         <v/>
       </c>
       <c r="AX60" s="49" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
     </row>
     <row r="62" spans="1:50" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C62" s="59" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="N62" s="60" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="AD62" s="60" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="AJ62" s="60" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="AL62" s="60" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="AM62" s="60" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="AO62" s="60" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="AQ62" s="60" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="AW62" s="60" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
     </row>
     <row r="63" spans="1:50" x14ac:dyDescent="0.2">
       <c r="C63" s="33" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="N63" s="61" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="P63" s="61" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="U63" s="61" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="X63" s="61" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="Z63" s="61" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="AC63" s="61" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="AH63" s="61" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="AJ63" s="61" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="AM63" s="61" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="AO63" s="61" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="AW63" s="61" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:50" x14ac:dyDescent="0.2">
       <c r="C64" s="62" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="3:49" hidden="1" x14ac:dyDescent="0.2">
       <c r="C65" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="N65">
         <f>IF(COUNTIF(Holidays!$A$2:$A$40,N$4)&gt;0,1,0)</f>
@@ -15164,12 +15266,12 @@
   </sheetData>
   <autoFilter ref="A4:M60" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <mergeCells count="8">
-    <mergeCell ref="AO3:AS3"/>
+    <mergeCell ref="AT3:AW3"/>
     <mergeCell ref="U3:Y3"/>
-    <mergeCell ref="AT3:AW3"/>
     <mergeCell ref="AJ3:AN3"/>
     <mergeCell ref="Z3:AD3"/>
     <mergeCell ref="N3:O3"/>
+    <mergeCell ref="AO3:AS3"/>
     <mergeCell ref="P3:T3"/>
     <mergeCell ref="AE3:AI3"/>
   </mergeCells>
@@ -15333,7 +15435,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -15343,48 +15445,52 @@
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="7" width="11" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="63" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="28" x14ac:dyDescent="0.2">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="F3" s="11" t="s">
         <v>14</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+        <v>337</v>
+      </c>
+      <c r="I3" s="80" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="64" t="s">
         <v>23</v>
       </c>
       <c r="B4" s="65" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="C4" s="65" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="D4" s="65">
         <f>COUNTIFS(Tasks!$D$5:$D$60,A4,Tasks!$B$5:$B$60,"&lt;&gt;P0",Tasks!$A$5:$A$60,"&lt;&gt;WP*")</f>
@@ -15396,26 +15502,29 @@
       </c>
       <c r="F4" s="65">
         <f>COUNTIFS(Tasks!$D$5:$D$60,A4,Tasks!$L$5:$L$60,"Completed",Tasks!$B$5:$B$60,"&lt;&gt;P0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="65">
         <f>COUNTIFS(Tasks!$D$5:$D$60,A4,Tasks!$L$5:$L$60,"In progress")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="65">
         <f>COUNTIFS(Tasks!$D$5:$D$60,A4,Tasks!$L$5:$L$60,"Incident")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="I4" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="66" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5" s="65" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="C5" s="65" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="D5" s="65">
         <f>COUNTIFS(Tasks!$D$5:$D$60,A5,Tasks!$B$5:$B$60,"&lt;&gt;P0",Tasks!$A$5:$A$60,"&lt;&gt;WP*")</f>
@@ -15431,22 +15540,25 @@
       </c>
       <c r="G5" s="65">
         <f>COUNTIFS(Tasks!$D$5:$D$60,A5,Tasks!$L$5:$L$60,"In progress")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" s="65">
         <f>COUNTIFS(Tasks!$D$5:$D$60,A5,Tasks!$L$5:$L$60,"Incident")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="I5" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="67" t="s">
         <v>17</v>
       </c>
       <c r="B6" s="65" t="s">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="C6" s="65" t="s">
-        <v>330</v>
+        <v>346</v>
       </c>
       <c r="D6" s="65">
         <f>COUNTIFS(Tasks!$D$5:$D$60,A6,Tasks!$B$5:$B$60,"&lt;&gt;P0",Tasks!$A$5:$A$60,"&lt;&gt;WP*")</f>
@@ -15458,26 +15570,29 @@
       </c>
       <c r="F6" s="65">
         <f>COUNTIFS(Tasks!$D$5:$D$60,A6,Tasks!$L$5:$L$60,"Completed",Tasks!$B$5:$B$60,"&lt;&gt;P0")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="65">
         <f>COUNTIFS(Tasks!$D$5:$D$60,A6,Tasks!$L$5:$L$60,"In progress")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" s="65">
         <f>COUNTIFS(Tasks!$D$5:$D$60,A6,Tasks!$L$5:$L$60,"Incident")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="I6" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="68" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="65" t="s">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="C7" s="65" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="D7" s="65">
         <f>COUNTIFS(Tasks!$D$5:$D$60,A7,Tasks!$B$5:$B$60,"&lt;&gt;P0",Tasks!$A$5:$A$60,"&lt;&gt;WP*")</f>
@@ -15493,22 +15608,25 @@
       </c>
       <c r="G7" s="65">
         <f>COUNTIFS(Tasks!$D$5:$D$60,A7,Tasks!$L$5:$L$60,"In progress")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" s="65">
         <f>COUNTIFS(Tasks!$D$5:$D$60,A7,Tasks!$L$5:$L$60,"Incident")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="I7" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="69" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B8" s="65" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="C8" s="65" t="s">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="D8" s="65">
         <f>COUNTIFS(Tasks!$D$5:$D$60,A8,Tasks!$B$5:$B$60,"&lt;&gt;P0",Tasks!$A$5:$A$60,"&lt;&gt;WP*")</f>
@@ -15528,12 +15646,15 @@
       </c>
       <c r="H8" s="65">
         <f>COUNTIFS(Tasks!$D$5:$D$60,A8,Tasks!$L$5:$L$60,"Incident")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+      <c r="I8" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="70" t="s">
-        <v>335</v>
+        <v>354</v>
       </c>
       <c r="D9" s="70">
         <f>SUM(D4:D8)</f>
@@ -15545,15 +15666,15 @@
       </c>
       <c r="F9" s="70">
         <f>SUM(F4:F8)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G9" s="70">
         <f>SUM(G4:G8)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H9" s="70">
         <f>SUM(H4:H8)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -15574,35 +15695,35 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="42" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>338</v>
+        <v>357</v>
       </c>
       <c r="E1" s="11" t="s">
         <v>9</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="65" t="s">
-        <v>340</v>
+        <v>359</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="C2" s="71">
         <v>46282</v>
@@ -15614,7 +15735,7 @@
         <v>14</v>
       </c>
       <c r="F2" s="65" t="s">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="G2" s="65">
         <f>IF(D2="","",IF(D2&gt;=C2,NETWORKDAYS(C2,D2,Holidays!$A$2:$A$40)-1,-(NETWORKDAYS(D2,C2,Holidays!$A$2:$A$40)-1)))</f>
@@ -15623,20 +15744,20 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="65" t="s">
-        <v>343</v>
+        <v>362</v>
       </c>
       <c r="B3" s="65" t="s">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="C3" s="71">
         <v>46304</v>
       </c>
       <c r="D3" s="72"/>
       <c r="E3" s="73" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F3" s="65" t="s">
-        <v>345</v>
+        <v>364</v>
       </c>
       <c r="G3" s="65" t="str">
         <f>IF(D3="","",IF(D3&gt;=C3,NETWORKDAYS(C3,D3,Holidays!$A$2:$A$40)-1,-(NETWORKDAYS(D3,C3,Holidays!$A$2:$A$40)-1)))</f>
@@ -15645,20 +15766,20 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="65" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="B4" s="65" t="s">
-        <v>347</v>
+        <v>366</v>
       </c>
       <c r="C4" s="71">
         <v>46314</v>
       </c>
       <c r="D4" s="72"/>
       <c r="E4" s="73" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F4" s="65" t="s">
-        <v>348</v>
+        <v>367</v>
       </c>
       <c r="G4" s="65" t="str">
         <f>IF(D4="","",IF(D4&gt;=C4,NETWORKDAYS(C4,D4,Holidays!$A$2:$A$40)-1,-(NETWORKDAYS(D4,C4,Holidays!$A$2:$A$40)-1)))</f>
@@ -15667,20 +15788,20 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="65" t="s">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="B5" s="65" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="C5" s="71">
         <v>46316</v>
       </c>
       <c r="D5" s="72"/>
       <c r="E5" s="73" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F5" s="65" t="s">
-        <v>351</v>
+        <v>370</v>
       </c>
       <c r="G5" s="65" t="str">
         <f>IF(D5="","",IF(D5&gt;=C5,NETWORKDAYS(C5,D5,Holidays!$A$2:$A$40)-1,-(NETWORKDAYS(D5,C5,Holidays!$A$2:$A$40)-1)))</f>
@@ -15689,20 +15810,20 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="65" t="s">
-        <v>352</v>
+        <v>371</v>
       </c>
       <c r="B6" s="65" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="C6" s="71">
         <v>46317</v>
       </c>
       <c r="D6" s="72"/>
       <c r="E6" s="73" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F6" s="65" t="s">
-        <v>354</v>
+        <v>373</v>
       </c>
       <c r="G6" s="65" t="str">
         <f>IF(D6="","",IF(D6&gt;=C6,NETWORKDAYS(C6,D6,Holidays!$A$2:$A$40)-1,-(NETWORKDAYS(D6,C6,Holidays!$A$2:$A$40)-1)))</f>
@@ -15711,20 +15832,20 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="65" t="s">
-        <v>355</v>
+        <v>374</v>
       </c>
       <c r="B7" s="65" t="s">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="C7" s="71">
         <v>46321</v>
       </c>
       <c r="D7" s="72"/>
       <c r="E7" s="73" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F7" s="65" t="s">
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="G7" s="65" t="str">
         <f>IF(D7="","",IF(D7&gt;=C7,NETWORKDAYS(C7,D7,Holidays!$A$2:$A$40)-1,-(NETWORKDAYS(D7,C7,Holidays!$A$2:$A$40)-1)))</f>
@@ -15733,20 +15854,20 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="65" t="s">
-        <v>358</v>
+        <v>377</v>
       </c>
       <c r="B8" s="65" t="s">
-        <v>359</v>
+        <v>378</v>
       </c>
       <c r="C8" s="71">
         <v>46323</v>
       </c>
       <c r="D8" s="72"/>
       <c r="E8" s="73" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F8" s="65" t="s">
-        <v>345</v>
+        <v>364</v>
       </c>
       <c r="G8" s="65" t="str">
         <f>IF(D8="","",IF(D8&gt;=C8,NETWORKDAYS(C8,D8,Holidays!$A$2:$A$40)-1,-(NETWORKDAYS(D8,C8,Holidays!$A$2:$A$40)-1)))</f>
@@ -15755,20 +15876,20 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="65" t="s">
-        <v>360</v>
+        <v>379</v>
       </c>
       <c r="B9" s="65" t="s">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="C9" s="71">
         <v>46331</v>
       </c>
       <c r="D9" s="72"/>
       <c r="E9" s="73" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F9" s="65" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="G9" s="65" t="str">
         <f>IF(D9="","",IF(D9&gt;=C9,NETWORKDAYS(C9,D9,Holidays!$A$2:$A$40)-1,-(NETWORKDAYS(D9,C9,Holidays!$A$2:$A$40)-1)))</f>
@@ -15802,227 +15923,237 @@
     <col min="11" max="11" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="63" t="s">
-        <v>363</v>
+        <v>382</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>366</v>
+        <v>385</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>368</v>
+        <v>387</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="H3" s="11" t="s">
         <v>9</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>369</v>
+        <v>388</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="K3" s="11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="28" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="74" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="C4" s="75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" s="75">
         <v>3</v>
       </c>
       <c r="E4" s="74">
-        <f t="shared" ref="E4:E13" si="0">C4*D4</f>
-        <v>9</v>
+        <f t="shared" ref="E4:E12" si="0">C4*D4</f>
+        <v>6</v>
       </c>
       <c r="F4" s="74" t="str">
-        <f t="shared" ref="F4:F13" si="1">IF(E4&gt;=6,"High",IF(E4&gt;=3,"Medium","Low"))</f>
+        <f t="shared" ref="F4:F12" si="1">IF(E4&gt;=6,"High",IF(E4&gt;=3,"Medium","Low"))</f>
         <v>High</v>
       </c>
       <c r="G4" s="20" t="s">
         <v>17</v>
       </c>
       <c r="H4" s="75" t="s">
-        <v>373</v>
+        <v>392</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="J4" s="76">
-        <v>46303</v>
-      </c>
-      <c r="K4" s="19"/>
-    </row>
-    <row r="5" spans="1:11" ht="28" x14ac:dyDescent="0.2">
+        <v>46313</v>
+      </c>
+      <c r="K4" s="19" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="74" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="C5" s="75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" s="75">
         <v>3</v>
       </c>
       <c r="E5" s="74">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F5" s="74" t="str">
         <f t="shared" si="1"/>
         <v>High</v>
       </c>
       <c r="G5" s="26" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H5" s="75" t="s">
-        <v>373</v>
+        <v>392</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>377</v>
+        <v>397</v>
       </c>
       <c r="J5" s="76">
-        <v>46303</v>
-      </c>
-      <c r="K5" s="19"/>
-    </row>
-    <row r="6" spans="1:11" ht="28" x14ac:dyDescent="0.2">
+        <v>46313</v>
+      </c>
+      <c r="K5" s="19" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="74" t="s">
-        <v>378</v>
+        <v>398</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>379</v>
+        <v>399</v>
       </c>
       <c r="C6" s="75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" s="75">
         <v>3</v>
       </c>
       <c r="E6" s="74">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F6" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="G6" s="25" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H6" s="75" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="J6" s="76">
-        <v>46303</v>
-      </c>
-      <c r="K6" s="19"/>
-    </row>
-    <row r="7" spans="1:11" ht="28" x14ac:dyDescent="0.2">
+        <v>46313</v>
+      </c>
+      <c r="K6" s="19" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="74" t="s">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>383</v>
+        <v>402</v>
       </c>
       <c r="C7" s="75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="75">
         <v>2</v>
       </c>
       <c r="E7" s="74">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F7" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H7" s="75" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="J7" s="76">
-        <v>46303</v>
-      </c>
-      <c r="K7" s="19"/>
-    </row>
-    <row r="8" spans="1:11" ht="28" x14ac:dyDescent="0.2">
+        <v>46313</v>
+      </c>
+      <c r="K7" s="19" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="74" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>387</v>
+        <v>405</v>
       </c>
       <c r="C8" s="75">
         <v>2</v>
       </c>
       <c r="D8" s="75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" s="74">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F8" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>High</v>
+        <v>Medium</v>
       </c>
       <c r="G8" s="25" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="H8" s="75" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>388</v>
+        <v>406</v>
       </c>
       <c r="J8" s="76">
-        <v>46303</v>
-      </c>
-      <c r="K8" s="19"/>
-    </row>
-    <row r="9" spans="1:11" ht="28" x14ac:dyDescent="0.2">
+        <v>46313</v>
+      </c>
+      <c r="K8" s="19" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="74" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="C9" s="75">
         <v>2</v>
@@ -16039,157 +16170,143 @@
         <v>Medium</v>
       </c>
       <c r="G9" s="26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H9" s="75" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>391</v>
+        <v>409</v>
       </c>
       <c r="J9" s="76">
-        <v>46303</v>
-      </c>
-      <c r="K9" s="19"/>
-    </row>
-    <row r="10" spans="1:11" ht="28" x14ac:dyDescent="0.2">
+        <v>46313</v>
+      </c>
+      <c r="K9" s="19" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="74" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="C10" s="75">
         <v>1</v>
       </c>
       <c r="D10" s="75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" s="74">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>Low</v>
+        <v>Medium</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H10" s="75" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="I10" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="J10" s="76">
+        <v>46313</v>
+      </c>
+      <c r="K10" s="19" t="s">
         <v>394</v>
       </c>
-      <c r="J10" s="76">
-        <v>46303</v>
-      </c>
-      <c r="K10" s="19"/>
-    </row>
-    <row r="11" spans="1:11" ht="28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="74" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>396</v>
+        <v>414</v>
       </c>
       <c r="C11" s="75">
+        <v>1</v>
+      </c>
+      <c r="D11" s="75">
         <v>2</v>
-      </c>
-      <c r="D11" s="75">
-        <v>3</v>
       </c>
       <c r="E11" s="74">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F11" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>High</v>
+        <v>Low</v>
       </c>
       <c r="G11" s="15" t="s">
         <v>13</v>
       </c>
       <c r="H11" s="75" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="J11" s="76">
-        <v>46303</v>
-      </c>
-      <c r="K11" s="19"/>
-    </row>
-    <row r="12" spans="1:11" ht="28" x14ac:dyDescent="0.2">
+        <v>46313</v>
+      </c>
+      <c r="K11" s="19" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="74" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="C12" s="75">
         <v>2</v>
       </c>
       <c r="D12" s="75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" s="74">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F12" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>Medium</v>
+        <v>Low</v>
       </c>
       <c r="G12" s="22" t="s">
         <v>23</v>
       </c>
       <c r="H12" s="75" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>400</v>
+        <v>418</v>
       </c>
       <c r="J12" s="76">
-        <v>46303</v>
-      </c>
-      <c r="K12" s="19"/>
-    </row>
-    <row r="13" spans="1:11" ht="28" x14ac:dyDescent="0.2">
-      <c r="A13" s="74" t="s">
-        <v>401</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>402</v>
-      </c>
-      <c r="C13" s="75">
-        <v>2</v>
-      </c>
-      <c r="D13" s="75">
-        <v>3</v>
-      </c>
-      <c r="E13" s="74">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="F13" s="74" t="str">
-        <f t="shared" si="1"/>
-        <v>High</v>
-      </c>
-      <c r="G13" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="H13" s="75" t="s">
-        <v>384</v>
-      </c>
-      <c r="I13" s="14" t="s">
-        <v>403</v>
-      </c>
-      <c r="J13" s="76">
-        <v>46303</v>
-      </c>
+        <v>46313</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="74"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="74"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="75"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="76"/>
       <c r="K13" s="19"/>
     </row>
   </sheetData>
@@ -16225,10 +16342,10 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>405</v>
+        <v>420</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -16236,10 +16353,10 @@
         <v>46289</v>
       </c>
       <c r="B2" s="78" t="s">
-        <v>406</v>
+        <v>421</v>
       </c>
       <c r="D2" s="79" t="s">
-        <v>407</v>
+        <v>422</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -16247,7 +16364,7 @@
         <v>46307</v>
       </c>
       <c r="B3" s="78" t="s">
-        <v>408</v>
+        <v>423</v>
       </c>
     </row>
   </sheetData>
